--- a/exports/trend_1d/AUBANK_full_report.xlsx
+++ b/exports/trend_1d/AUBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>24.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43130</v>
+        <v>43131</v>
       </c>
       <c r="H2" t="n">
-        <v>339.65</v>
+        <v>328.25</v>
       </c>
       <c r="I2" t="n">
         <v>329.8151945793842</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K2" t="n">
-        <v>15.84</v>
+        <v>11.95</v>
       </c>
       <c r="L2" t="n">
         <v>15.38</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.79</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43185</v>
+        <v>43186</v>
       </c>
       <c r="H3" t="n">
-        <v>295.3</v>
+        <v>311.35</v>
       </c>
       <c r="I3" t="n">
         <v>310.3981703096479</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>10.04</v>
+        <v>5.15</v>
       </c>
       <c r="L3" t="n">
         <v>2.97</v>
@@ -612,7 +647,7 @@
         <v>4.21</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9</v>
+        <v>5.44</v>
       </c>
       <c r="O3" t="n">
         <v>-3.36</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.17</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43287</v>
+        <v>43290</v>
       </c>
       <c r="H4" t="n">
-        <v>339.65</v>
+        <v>318.8</v>
       </c>
       <c r="I4" t="n">
         <v>327.8191107573115</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K4" t="n">
-        <v>9.09</v>
+        <v>2.39</v>
       </c>
       <c r="L4" t="n">
         <v>5.25</v>
@@ -669,7 +716,7 @@
         <v>4.36</v>
       </c>
       <c r="N4" t="n">
-        <v>2.79</v>
+        <v>6.14</v>
       </c>
       <c r="O4" t="n">
         <v>5.44</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>15.77</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43321</v>
+        <v>43322</v>
       </c>
       <c r="H5" t="n">
-        <v>322.25</v>
+        <v>346.85</v>
       </c>
       <c r="I5" t="n">
         <v>342.9041647178703</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.08</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>5.08</v>
+        <v>11.98</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8</v>
+        <v>3.96</v>
       </c>
       <c r="N5" t="n">
-        <v>2.06</v>
+        <v>7.63</v>
       </c>
       <c r="O5" t="n">
         <v>-6.14</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.81</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H6" t="n">
-        <v>337.95</v>
+        <v>322.45</v>
       </c>
       <c r="I6" t="n">
         <v>333.6838619500601</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.57</v>
+        <v>-7.03</v>
       </c>
       <c r="L6" t="n">
-        <v>3.96</v>
+        <v>7.77</v>
       </c>
       <c r="M6" t="n">
         <v>1.35</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>4.59</v>
       </c>
       <c r="O6" t="n">
         <v>7.63</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.75</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43430</v>
+        <v>43431</v>
       </c>
       <c r="H7" t="n">
-        <v>294.95</v>
+        <v>304.5</v>
       </c>
       <c r="I7" t="n">
         <v>303.9648526135713</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K7" t="n">
-        <v>8.529999999999999</v>
+        <v>5.57</v>
       </c>
       <c r="L7" t="n">
         <v>6.12</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>14.09</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43486</v>
+        <v>43487</v>
       </c>
       <c r="H8" t="n">
-        <v>304.35</v>
+        <v>297.65</v>
       </c>
       <c r="I8" t="n">
         <v>298.4010792497671</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.05</v>
+        <v>-2.25</v>
       </c>
       <c r="L8" t="n">
         <v>8.26</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.76</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43538</v>
+        <v>43539</v>
       </c>
       <c r="H9" t="n">
-        <v>295.7</v>
+        <v>305.45</v>
       </c>
       <c r="I9" t="n">
         <v>304.3698437096671</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K9" t="n">
-        <v>0.66</v>
+        <v>-2.62</v>
       </c>
       <c r="L9" t="n">
         <v>5.53</v>
@@ -954,7 +1061,7 @@
         <v>1.33</v>
       </c>
       <c r="N9" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>-2.2</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.69</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43655</v>
+        <v>43656</v>
       </c>
       <c r="H10" t="n">
-        <v>331.9</v>
+        <v>328.3</v>
       </c>
       <c r="I10" t="n">
         <v>328.9692561711775</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K10" t="n">
-        <v>8.66</v>
+        <v>7.48</v>
       </c>
       <c r="L10" t="n">
         <v>11.41</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>11.28</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43777</v>
+        <v>43780</v>
       </c>
       <c r="H11" t="n">
-        <v>344.75</v>
+        <v>359.2</v>
       </c>
       <c r="I11" t="n">
         <v>348.6398458006115</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.01</v>
+        <v>-9.41</v>
       </c>
       <c r="L11" t="n">
-        <v>8.59</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>4.08</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.58</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43899</v>
+        <v>43901</v>
       </c>
       <c r="H12" t="n">
-        <v>531.5</v>
+        <v>514.7</v>
       </c>
       <c r="I12" t="n">
         <v>519.502147631394</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K12" t="n">
-        <v>47.97</v>
+        <v>43.29</v>
       </c>
       <c r="L12" t="n">
         <v>4.65</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>21.25</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43985</v>
+        <v>43986</v>
       </c>
       <c r="H13" t="n">
-        <v>225.95</v>
+        <v>236.85</v>
       </c>
       <c r="I13" t="n">
         <v>230.744421980452</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" t="n">
-        <v>56.1</v>
+        <v>53.98</v>
       </c>
       <c r="L13" t="n">
         <v>4.63</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>18.32</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H14" t="n">
-        <v>368.35</v>
+        <v>334</v>
       </c>
       <c r="I14" t="n">
         <v>342.4981579418781</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K14" t="n">
-        <v>55.52</v>
+        <v>41.02</v>
       </c>
       <c r="L14" t="n">
         <v>7.05</v>
@@ -1239,7 +1406,7 @@
         <v>4.98</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>9.33</v>
       </c>
       <c r="O14" t="n">
         <v>4.82</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>19.48</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H15" t="n">
-        <v>335.2</v>
+        <v>367.2</v>
       </c>
       <c r="I15" t="n">
         <v>363.7132285823367</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.36</v>
+        <v>-9.94</v>
       </c>
       <c r="L15" t="n">
         <v>12.51</v>
@@ -1296,7 +1475,7 @@
         <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>4.94</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>-9.33</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>16.87</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H16" t="n">
-        <v>587.25</v>
+        <v>538.25</v>
       </c>
       <c r="I16" t="n">
         <v>543.2878934007283</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K16" t="n">
-        <v>59.93</v>
+        <v>46.58</v>
       </c>
       <c r="L16" t="n">
         <v>8.09</v>
@@ -1353,7 +1544,7 @@
         <v>3.51</v>
       </c>
       <c r="N16" t="n">
-        <v>6.31</v>
+        <v>8.34</v>
       </c>
       <c r="O16" t="n">
         <v>9.550000000000001</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>22.03</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44375</v>
+        <v>44376</v>
       </c>
       <c r="H17" t="n">
-        <v>525.2</v>
+        <v>538.65</v>
       </c>
       <c r="I17" t="n">
         <v>538.4367840602022</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K17" t="n">
-        <v>2.42</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>8.869999999999999</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.84</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H18" t="n">
-        <v>647.45</v>
+        <v>565.35</v>
       </c>
       <c r="I18" t="n">
         <v>611.0628802240892</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K18" t="n">
-        <v>20.2</v>
+        <v>4.96</v>
       </c>
       <c r="L18" t="n">
         <v>5.32</v>
@@ -1467,7 +1682,7 @@
         <v>2.37</v>
       </c>
       <c r="N18" t="n">
-        <v>5.01</v>
+        <v>12.68</v>
       </c>
       <c r="O18" t="n">
         <v>2.56</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>24.38</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44494</v>
+        <v>44495</v>
       </c>
       <c r="H19" t="n">
-        <v>601.2</v>
+        <v>630.45</v>
       </c>
       <c r="I19" t="n">
         <v>617.4793341155416</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.34</v>
+        <v>-11.51</v>
       </c>
       <c r="L19" t="n">
         <v>15.61</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>12.85</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H20" t="n">
-        <v>595.45</v>
+        <v>563.95</v>
       </c>
       <c r="I20" t="n">
         <v>566.5391872203013</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.55</v>
+        <v>-10.55</v>
       </c>
       <c r="L20" t="n">
-        <v>10.23</v>
+        <v>11.25</v>
       </c>
       <c r="M20" t="n">
         <v>1.36</v>
       </c>
       <c r="N20" t="n">
-        <v>3.16</v>
+        <v>5.29</v>
       </c>
       <c r="O20" t="n">
         <v>4.87</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>14.82</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H21" t="n">
-        <v>547.95</v>
+        <v>584.65</v>
       </c>
       <c r="I21" t="n">
         <v>567.2451590538714</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K21" t="n">
-        <v>2.84</v>
+        <v>-3.67</v>
       </c>
       <c r="L21" t="n">
-        <v>5.95</v>
+        <v>10.77</v>
       </c>
       <c r="M21" t="n">
-        <v>1.74</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.71</v>
+        <v>6.7</v>
       </c>
       <c r="O21" t="n">
         <v>-5.29</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>13.88</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H22" t="n">
-        <v>636.7</v>
+        <v>589.75</v>
       </c>
       <c r="I22" t="n">
         <v>620.4580860606768</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K22" t="n">
-        <v>8.9</v>
+        <v>0.87</v>
       </c>
       <c r="L22" t="n">
         <v>4.55</v>
       </c>
       <c r="M22" t="n">
-        <v>2.28</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>5.04</v>
+        <v>7.37</v>
       </c>
       <c r="O22" t="n">
         <v>6.7</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.11</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44650</v>
+        <v>44651</v>
       </c>
       <c r="H23" t="n">
-        <v>601.1</v>
+        <v>623.1</v>
       </c>
       <c r="I23" t="n">
         <v>621.434808847427</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.92</v>
+        <v>-5.65</v>
       </c>
       <c r="L23" t="n">
         <v>7.24</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.65</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H24" t="n">
-        <v>658.2</v>
+        <v>639.6</v>
       </c>
       <c r="I24" t="n">
         <v>653.1637717489168</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K24" t="n">
-        <v>5.63</v>
+        <v>2.65</v>
       </c>
       <c r="L24" t="n">
         <v>3.22</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>13.39</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44774</v>
+        <v>44775</v>
       </c>
       <c r="H25" t="n">
-        <v>604.75</v>
+        <v>617.8</v>
       </c>
       <c r="I25" t="n">
         <v>611.5593497276852</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K25" t="n">
-        <v>5.45</v>
+        <v>3.41</v>
       </c>
       <c r="L25" t="n">
         <v>5.93</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>10.13</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H26" t="n">
-        <v>637.85</v>
+        <v>597.15</v>
       </c>
       <c r="I26" t="n">
         <v>633.9151017961931</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K26" t="n">
-        <v>3.25</v>
+        <v>-3.34</v>
       </c>
       <c r="L26" t="n">
-        <v>3.37</v>
+        <v>4.56</v>
       </c>
       <c r="M26" t="n">
         <v>2.17</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>6.38</v>
       </c>
       <c r="O26" t="n">
         <v>2.16</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>13.28</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44872</v>
+        <v>44874</v>
       </c>
       <c r="H27" t="n">
-        <v>616.35</v>
+        <v>642.55</v>
       </c>
       <c r="I27" t="n">
         <v>636.1298167148919</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.22</v>
+        <v>-7.6</v>
       </c>
       <c r="L27" t="n">
-        <v>6.97</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>3.39</v>
       </c>
       <c r="N27" t="n">
-        <v>4.08</v>
+        <v>4.25</v>
       </c>
       <c r="O27" t="n">
         <v>-6.38</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.92</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44930</v>
+        <v>44931</v>
       </c>
       <c r="H28" t="n">
-        <v>641.6</v>
+        <v>636.1</v>
       </c>
       <c r="I28" t="n">
         <v>636.9124992557471</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.15</v>
+        <v>-1</v>
       </c>
       <c r="L28" t="n">
         <v>5.77</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>7.4</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45028</v>
+        <v>45029</v>
       </c>
       <c r="H29" t="n">
-        <v>580.15</v>
+        <v>679.2</v>
       </c>
       <c r="I29" t="n">
         <v>607.5446061829601</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K29" t="n">
-        <v>8.800000000000001</v>
+        <v>-6.78</v>
       </c>
       <c r="L29" t="n">
-        <v>2.64</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>1.47</v>
+        <v>8.59</v>
       </c>
       <c r="N29" t="n">
-        <v>3.98</v>
+        <v>17.07</v>
       </c>
       <c r="O29" t="n">
         <v>-0.86</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>14.96</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45131</v>
+        <v>45132</v>
       </c>
       <c r="H30" t="n">
-        <v>739.15</v>
+        <v>731.3</v>
       </c>
       <c r="I30" t="n">
         <v>732.3174227006797</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K30" t="n">
-        <v>8.83</v>
+        <v>7.67</v>
       </c>
       <c r="L30" t="n">
         <v>7.98</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45187</v>
+        <v>45189</v>
       </c>
       <c r="H31" t="n">
-        <v>729.05</v>
+        <v>755.45</v>
       </c>
       <c r="I31" t="n">
         <v>750.5729595120075</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K31" t="n">
-        <v>0.31</v>
+        <v>-3.3</v>
       </c>
       <c r="L31" t="n">
-        <v>2.83</v>
+        <v>3.82</v>
       </c>
       <c r="M31" t="n">
         <v>1.27</v>
       </c>
       <c r="N31" t="n">
-        <v>2.77</v>
+        <v>3.62</v>
       </c>
       <c r="O31" t="n">
         <v>-1.06</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45218</v>
+        <v>45219</v>
       </c>
       <c r="H32" t="n">
-        <v>705.15</v>
+        <v>699.8</v>
       </c>
       <c r="I32" t="n">
         <v>701.8015099144909</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.66</v>
+        <v>-7.37</v>
       </c>
       <c r="L32" t="n">
         <v>8.93</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>5.58</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45242</v>
+        <v>45243</v>
       </c>
       <c r="H33" t="n">
-        <v>708</v>
+        <v>729.75</v>
       </c>
       <c r="I33" t="n">
         <v>715.9206167193095</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.17</v>
+        <v>-4.28</v>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>4.66</v>
       </c>
       <c r="M33" t="n">
         <v>1.37</v>
       </c>
       <c r="N33" t="n">
-        <v>2.25</v>
+        <v>3.07</v>
       </c>
       <c r="O33" t="n">
         <v>-0.76</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.91</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45309</v>
+        <v>45310</v>
       </c>
       <c r="H34" t="n">
-        <v>734.1</v>
+        <v>730.55</v>
       </c>
       <c r="I34" t="n">
         <v>732.7999310026626</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6</v>
+        <v>0.11</v>
       </c>
       <c r="L34" t="n">
         <v>3.47</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H35" t="n">
-        <v>591.6</v>
+        <v>605.05</v>
       </c>
       <c r="I35" t="n">
         <v>602.9496178247318</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K35" t="n">
-        <v>19.02</v>
+        <v>17.18</v>
       </c>
       <c r="L35" t="n">
         <v>3.76</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.17</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45513</v>
+        <v>45516</v>
       </c>
       <c r="H36" t="n">
-        <v>625.95</v>
+        <v>609.75</v>
       </c>
       <c r="I36" t="n">
         <v>623.5688987484939</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K36" t="n">
-        <v>3.45</v>
+        <v>0.78</v>
       </c>
       <c r="L36" t="n">
         <v>4.69</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>8.85</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45533</v>
+        <v>45534</v>
       </c>
       <c r="H37" t="n">
-        <v>640.35</v>
+        <v>688.7</v>
       </c>
       <c r="I37" t="n">
         <v>655.8705369314497</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.02</v>
+        <v>-12.95</v>
       </c>
       <c r="L37" t="n">
-        <v>6.5</v>
+        <v>14.31</v>
       </c>
       <c r="M37" t="n">
         <v>1.09</v>
       </c>
       <c r="N37" t="n">
-        <v>1.68</v>
+        <v>7.55</v>
       </c>
       <c r="O37" t="n">
         <v>-2.59</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.66</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45575</v>
+        <v>45576</v>
       </c>
       <c r="H38" t="n">
-        <v>699.95</v>
+        <v>690.4</v>
       </c>
       <c r="I38" t="n">
         <v>690.7133476332546</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K38" t="n">
-        <v>1.63</v>
+        <v>0.25</v>
       </c>
       <c r="L38" t="n">
         <v>6.85</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="H39" t="n">
-        <v>575.1</v>
+        <v>586.95</v>
       </c>
       <c r="I39" t="n">
         <v>586.6288331751753</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K39" t="n">
-        <v>16.7</v>
+        <v>14.98</v>
       </c>
       <c r="L39" t="n">
         <v>2.56</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45699</v>
+        <v>45700</v>
       </c>
       <c r="H40" t="n">
-        <v>570.7</v>
+        <v>554.4</v>
       </c>
       <c r="I40" t="n">
         <v>554.9355258012416</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.77</v>
+        <v>-5.55</v>
       </c>
       <c r="L40" t="n">
         <v>7.32</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.82</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H41" t="n">
-        <v>542.8</v>
+        <v>550.05</v>
       </c>
       <c r="I41" t="n">
         <v>549.7109076298284</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K41" t="n">
-        <v>2.09</v>
+        <v>0.78</v>
       </c>
       <c r="L41" t="n">
         <v>3.08</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.85</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45856</v>
+        <v>45859</v>
       </c>
       <c r="H42" t="n">
-        <v>794.9</v>
+        <v>752.9</v>
       </c>
       <c r="I42" t="n">
         <v>776.6270859490908</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K42" t="n">
-        <v>44.51</v>
+        <v>36.88</v>
       </c>
       <c r="L42" t="n">
         <v>6.64</v>
@@ -2835,7 +3338,7 @@
         <v>6.72</v>
       </c>
       <c r="N42" t="n">
-        <v>3.89</v>
+        <v>5.28</v>
       </c>
       <c r="O42" t="n">
         <v>1.34</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H43" t="n">
-        <v>741.9</v>
+        <v>762.95</v>
       </c>
       <c r="I43" t="n">
         <v>743.9273328089876</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K43" t="n">
-        <v>1.46</v>
+        <v>-1.33</v>
       </c>
       <c r="L43" t="n">
         <v>6.26</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.23</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="H44" t="n">
-        <v>966.1</v>
+        <v>963.55</v>
       </c>
       <c r="I44" t="n">
         <v>963.5749959782889</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K44" t="n">
-        <v>26.63</v>
+        <v>26.29</v>
       </c>
       <c r="L44" t="n">
         <v>2.35</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.23</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H45" t="n">
-        <v>888.45</v>
+        <v>967.8</v>
       </c>
       <c r="I45" t="n">
         <v>961.7680298594109</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K45" t="n">
-        <v>7.79</v>
+        <v>-0.44</v>
       </c>
       <c r="L45" t="n">
         <v>7.85</v>
       </c>
       <c r="M45" t="n">
-        <v>2.05</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>3.82</v>
+        <v>8.93</v>
       </c>
       <c r="O45" t="n">
         <v>-0.26</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>14.79</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="H46" t="n">
-        <v>974</v>
+        <v>958.7</v>
       </c>
       <c r="I46" t="n">
         <v>970.8458113637396</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>0.64</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L46" t="n">
         <v>5.1</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.35</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="H47" t="n">
-        <v>1033.05</v>
+        <v>1045.05</v>
       </c>
       <c r="I47" t="n">
         <v>1036.92542628314</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.76</v>
+        <v>-9.01</v>
       </c>
       <c r="L47" t="n">
         <v>10.15</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.5</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="H48" t="n">
-        <v>1003.3</v>
+        <v>980.2</v>
       </c>
       <c r="I48" t="n">
         <v>988.4165340265164</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K48" t="n">
-        <v>-4</v>
+        <v>-6.21</v>
       </c>
       <c r="L48" t="n">
-        <v>5.31</v>
+        <v>6.64</v>
       </c>
       <c r="M48" t="n">
         <v>1.48</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="H49" t="n">
-        <v>1047.3</v>
+        <v>1060</v>
       </c>
       <c r="I49" t="n">
         <v>1053.162956080011</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.85</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L49" t="n">
         <v>9.039999999999999</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H50" t="n">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="I50" t="n">
         <v>1053.422120998868</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>0.47</v>
+        <v>-0.66</v>
       </c>
       <c r="L50" t="n">
         <v>2.34</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3351,6 +3962,14 @@
       <c r="Q51" t="n">
         <v>35</v>
       </c>
+      <c r="R51" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7289,7 +7908,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -7299,7 +7918,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -7309,7 +7928,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -7319,7 +7938,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -7329,7 +7948,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -7339,7 +7958,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116.6</v>
+        <v>119.4</v>
       </c>
     </row>
     <row r="11">
@@ -7349,7 +7968,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -7359,7 +7978,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -7369,7 +7988,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="14">
@@ -7379,7 +7998,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.23</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="15">
@@ -7389,7 +8008,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="16">
@@ -7399,7 +8018,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.31</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="17">
@@ -7409,7 +8028,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>59.93</v>
+        <v>53.98</v>
       </c>
     </row>
     <row r="18">
@@ -7419,7 +8038,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="19">
@@ -7429,7 +8048,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.34</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="20">
@@ -7439,7 +8058,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.93</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="21">
@@ -7459,7 +8078,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -7469,7 +8088,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -7479,7 +8098,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.79</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="25">
@@ -7489,7 +8108,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.64</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="26">
@@ -7499,7 +8118,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.13</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="27">
@@ -7509,7 +8128,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.43</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="28">
@@ -7519,7 +8138,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
